--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_16-10-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_16-10-2025.xlsx
@@ -518,17 +518,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -595,17 +595,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -638,25 +638,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -696,17 +696,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -739,25 +739,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -797,17 +797,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -840,25 +840,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -898,17 +898,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -941,25 +941,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1042,25 +1042,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£20.90</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£20.90</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1143,25 +1143,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1201,17 +1201,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1244,25 +1244,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1345,25 +1345,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1547,25 +1547,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1648,25 +1648,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1826,25 +1826,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1884,17 +1884,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1927,25 +1927,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1985,17 +1985,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2028,25 +2028,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
